--- a/기능정의서.xlsx
+++ b/기능정의서.xlsx
@@ -159,7 +159,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -273,11 +273,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00003DA5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00003DA5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -393,6 +417,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -768,7 +794,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DARK Factory – VNB Assistant
+          <t>VNB Assistant
 기능 정의서</t>
         </is>
       </c>
@@ -802,7 +828,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>DARK Factory – VNB Assistant</t>
+          <t>VNB Assistant</t>
         </is>
       </c>
     </row>
@@ -1085,6 +1111,12 @@
           <t xml:space="preserve">  ❑ 1. 보종별 예측 모델 매핑</t>
         </is>
       </c>
+      <c r="B3" s="43" t="n"/>
+      <c r="C3" s="43" t="n"/>
+      <c r="D3" s="43" t="n"/>
+      <c r="E3" s="43" t="n"/>
+      <c r="F3" s="43" t="n"/>
+      <c r="G3" s="44" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
@@ -1325,6 +1357,12 @@
           <t xml:space="preserve">  ❑ 2. 집계 기준 데이터 (AGG_UNIT_DATA / aggData)</t>
         </is>
       </c>
+      <c r="B37" s="43" t="n"/>
+      <c r="C37" s="43" t="n"/>
+      <c r="D37" s="43" t="n"/>
+      <c r="E37" s="43" t="n"/>
+      <c r="F37" s="43" t="n"/>
+      <c r="G37" s="44" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
@@ -1481,6 +1519,12 @@
           <t xml:space="preserve">  ❑ 3. 히트맵 차원 및 가중치 (HEATMAP_DIMS / DIM_WEIGHTS)</t>
         </is>
       </c>
+      <c r="B46" s="43" t="n"/>
+      <c r="C46" s="43" t="n"/>
+      <c r="D46" s="43" t="n"/>
+      <c r="E46" s="43" t="n"/>
+      <c r="F46" s="43" t="n"/>
+      <c r="G46" s="44" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
@@ -1525,6 +1569,9 @@
           <t>1.00 / 0.85 / 0.72 / 0.95</t>
         </is>
       </c>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="10" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="B50" s="24" t="inlineStr">
@@ -1542,6 +1589,9 @@
           <t>1.00 / 0.62 / 0.38 / 0.87</t>
         </is>
       </c>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="10" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="B51" s="20" t="inlineStr">
@@ -1559,6 +1609,9 @@
           <t>0.62 / 0.92 / 1.00 / 0.85 / 0.57</t>
         </is>
       </c>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="10" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="B52" s="24" t="inlineStr">
@@ -1576,6 +1629,9 @@
           <t>1.00 / 0.82</t>
         </is>
       </c>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="10" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="B53" s="20" t="inlineStr">
@@ -1593,6 +1649,9 @@
           <t>0.72 / 0.87 / 1.00 / 1.14</t>
         </is>
       </c>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="10" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="B54" s="24" t="inlineStr">
@@ -1610,6 +1669,9 @@
           <t>0.68 / 0.84 / 1.00 / 1.18</t>
         </is>
       </c>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="10" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
@@ -1617,6 +1679,12 @@
           <t xml:space="preserve">  ❑ 4. 공통 UI 컴포넌트</t>
         </is>
       </c>
+      <c r="B56" s="43" t="n"/>
+      <c r="C56" s="43" t="n"/>
+      <c r="D56" s="43" t="n"/>
+      <c r="E56" s="43" t="n"/>
+      <c r="F56" s="43" t="n"/>
+      <c r="G56" s="44" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
@@ -1661,6 +1729,9 @@
           <t>섹션 번호 뱃지 + 제목 + 설명</t>
         </is>
       </c>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="10" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="B60" s="24" t="inlineStr">
@@ -1678,6 +1749,9 @@
           <t>KPI 카드 (아이콘 + 숫자 + 서브텍스트)</t>
         </is>
       </c>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="10" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="B61" s="20" t="inlineStr">
@@ -1695,6 +1769,9 @@
           <t>재학습 트리거 조건 행</t>
         </is>
       </c>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="10" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="B62" s="24" t="inlineStr">
@@ -1712,6 +1789,9 @@
           <t>키-값 행 (모델 메타정보)</t>
         </is>
       </c>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="9" t="n"/>
+      <c r="G62" s="10" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="B63" s="20" t="inlineStr">
@@ -1729,6 +1809,9 @@
           <t>결과 박스 (accent=강조 vs 일반)</t>
         </is>
       </c>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="10" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="B64" s="24" t="inlineStr">
@@ -1746,6 +1829,9 @@
           <t>변경 영향 분석 슬라이더 행</t>
         </is>
       </c>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="9" t="n"/>
+      <c r="G64" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -1783,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2125,182 @@
         </is>
       </c>
       <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TAB6 대시보드</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>드래그앤드롭 위젯 그리드 전면 도입 (react-grid-layout legacy + WidthProvider)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>개편</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TAB6 대시보드</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>사용자 정의 차트 빌더 추가 (막대/선형/면적/원형/히트맵 5종)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TAB6 대시보드</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>글로벌 필터 바 추가 (기준분기·보종·채널 콤보박스)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>사이드바</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>"DB 관리" 그룹 신설, VNB예측모델 개발 등 상위 항목 분리, 토글 좌측 "메뉴" 레이블 추가</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>우측 고정 패널 → 플로팅 버튼 + 슬라이드 드로어 방식 전환 (메인 콘텐츠를 밀어냄)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>개편</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>탭 바</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>빈 상태 자리표시자 텍스트 제거</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>프로젝트명 "DARK Factory" 제거, "VNB Assistant"로 통일</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>기능정의서</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>README·기능정의서.md·기능정의서.xlsx 현행화</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
@@ -2069,12 +2331,13 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>DARK Factory – VNB Assistant  |  기능 목록</t>
+          <t>VNB Assistant  |  기능 목록</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
       <c r="C1" s="10" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -2174,7 +2437,7 @@
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>좌측 사이드바에 VNB Assistant 7개 메뉴와 기타 도구를 트리 구조로 표시. 클릭 시 해당 탭을 워크스페이스에 오픈</t>
+          <t>좌측 사이드바에 "DB 관리" 그룹(학습용DB·예측용DB·예측결과저장DB)과 VNB예측모델 개발·시뮬레이션·대시보드·출력·기타 도구를 계층 구조로 표시. 클릭 시 해당 탭을 워크스페이스에 오픈</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2471,12 @@
       <c r="A12" s="42" t="n"/>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>우측 패널 접기/펼치기</t>
+          <t>AI 어시스턴트 챗봇</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>우측 정보 패널의 접기/펼치기 버튼으로 화면 공간 조절 가능</t>
+          <t>우하단 플로팅 챗봇 버튼 클릭 시 AI 어시스턴트 패널이 우측 슬라이드로 열림. 메인 콘텐츠가 왼쪽으로 밀림. 패널 X 버튼으로 닫기</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2807,12 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>VNB 결산 DB vs 예측 모델 트렌드 조회</t>
+          <t>위젯 그리드 조회 및 조작</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>보종 Select(전체/암보험/종신/연금/건강) → 2025Q1~2026Q2 분기별 결산 DB와 예측 모델 VNB 추이를 LineChart로 비교. 미래 분기는 예측 모델값만 점선으로 표시</t>
+          <t>글로벌 필터(기준분기·보종·채널) 적용, KPI카드·트렌드·Bar 기본 3종 위젯 표시. 드래그로 이동, 핸들로 리사이즈, X로 삭제, 초기화 버튼으로 복원</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2820,12 @@
       <c r="A37" s="41" t="n"/>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>동일가입조건 결산 DB vs 예측 모델 비교</t>
+          <t>사용자 정의 차트 빌더</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>보종 Select → 동일한 가입조건(MP) 기준으로 결산 DB 집계 VNB와 예측 모델 VNB를 나란히 비교. 차이·MAPE 함께 표시</t>
+          <t>"차트 추가" → 유형 선택(막대/선형/면적/원형/히트맵) → 축 구성(X차원·Y지표·그룹차원) → 자동 제목 생성 후 위젯 추가</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2833,12 @@
       <c r="A38" s="41" t="n"/>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>사용자 조건 VNB 예측·집계 시뮬레이션</t>
+          <t>위젯 드래그앤드롭</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>가입조건 입력 후 시뮬레이션 실행 → 보종별 예측 모델로 VNB 즉시 산출 → 결산 DB 동일조건 집계값과 차이·MAPE·신계약마진율 비교</t>
+          <t>react-grid-layout 기반 위젯 자유 배치. 헤더(≡) 드래그로 이동, 우하단 핸들 드래그로 크기 조절</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2846,12 @@
       <c r="A39" s="42" t="n"/>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>판매속성별 VNB 히트맵 조회</t>
+          <t>판매속성별 VNB 히트맵</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>행·열 축을 채널/보종/연령대/성별/납기/보험기간 6개 차원 중 자유 선택 → 해당 조합별 VNB 값을 Blue 계열 색상으로 즉시 생성</t>
+          <t>행·열 축을 채널/보종/연령대/성별/납기/분기 6개 차원 중 자유 선택 → DIM_WEIGHTS 가중치 곱 기반 VNB. Blue 계열 9단계 색상 매핑</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2975,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>DARK Factory – VNB Assistant  |  시스템 개요</t>
+          <t>VNB Assistant  |  시스템 개요</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
@@ -2721,6 +2984,7 @@
       <c r="E1" s="9" t="n"/>
       <c r="F1" s="10" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2736,9 +3000,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>DARK Factory – VNB Assistant</t>
-        </is>
-      </c>
+          <t>VNB Assistant</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
@@ -2751,6 +3019,10 @@
           <t>보험 VNB 예측 모델 학습·시뮬레이션·집계 플랫폼</t>
         </is>
       </c>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
@@ -2763,6 +3035,10 @@
           <t>신한라이프 상품개발팀</t>
         </is>
       </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="10" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -2772,9 +3048,13 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>React 19 + TypeScript 5.7 + Vite 6</t>
-        </is>
-      </c>
+          <t>React 19 + TypeScript 5.7 + Vite 6 · react-grid-layout 2.2</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="10" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -2787,6 +3067,10 @@
           <t>Tailwind CSS 3 + shadcn/ui</t>
         </is>
       </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -2796,9 +3080,13 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Recharts 3.9 (BarChart, LineChart)</t>
-        </is>
-      </c>
+          <t>Recharts 3.9 (BarChart, LineChart, PieChart)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -2811,6 +3099,10 @@
           <t>FastAPI 0.138 / Uvicorn 0.49 / Pydantic 2.13 – 미연결 시 로컬 폴백</t>
         </is>
       </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -2823,7 +3115,12 @@
           <t>로컬 Vite 개발 / Docker Compose / GitHub Pages (정적)</t>
         </is>
       </c>
-    </row>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
@@ -3200,11 +3497,16 @@
           <t>408개</t>
         </is>
       </c>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
       <c r="E4" s="7" t="inlineStr">
         <is>
           <t>6개 카테고리</t>
         </is>
       </c>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -3217,11 +3519,16 @@
           <t>410만건</t>
         </is>
       </c>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="10" t="n"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>누적 적재</t>
         </is>
       </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -3234,11 +3541,16 @@
           <t>5개</t>
         </is>
       </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>배치 3 / 실시간 2</t>
         </is>
       </c>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
@@ -3246,6 +3558,13 @@
           <t xml:space="preserve">  ❑ 1. 설명변수 DB 구축 및 관리</t>
         </is>
       </c>
+      <c r="B8" s="43" t="n"/>
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="43" t="n"/>
+      <c r="E8" s="43" t="n"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="43" t="n"/>
+      <c r="H8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -3437,6 +3756,13 @@
           <t xml:space="preserve">  ❑ 2. 학습 데이터 생성</t>
         </is>
       </c>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="43" t="n"/>
+      <c r="D18" s="43" t="n"/>
+      <c r="E18" s="43" t="n"/>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="43" t="n"/>
+      <c r="H18" s="44" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
@@ -3456,6 +3782,11 @@
           <t>Button + Progress(shadcn/ui) + Recharts BarChart</t>
         </is>
       </c>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
@@ -3468,6 +3799,11 @@
           <t>isGenerating(bool), genProgress(0~100)</t>
         </is>
       </c>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="10" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
@@ -3480,6 +3816,11 @@
           <t>'학습데이터 대량 생성' 버튼 → 50ms 인터벌로 progress 증가 → 100 도달 시 완료</t>
         </is>
       </c>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="10" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="B23" s="12" t="inlineStr">
@@ -3492,6 +3833,11 @@
           <t>monthlyData: 최근 6개월 학습 건수 (단위: 만건)</t>
         </is>
       </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="10" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
@@ -3499,6 +3845,13 @@
           <t xml:space="preserve">  ❑ 3. 데이터 품질 지표</t>
         </is>
       </c>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="43" t="n"/>
+      <c r="D25" s="43" t="n"/>
+      <c r="E25" s="43" t="n"/>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="43" t="n"/>
+      <c r="H25" s="44" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
@@ -3737,11 +4090,11 @@
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="C21:H21"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="B4:D4"/>
@@ -3815,11 +4168,16 @@
           <t>5,999만</t>
         </is>
       </c>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
       <c r="E4" s="7" t="inlineStr">
         <is>
           <t>전체 보종 합산</t>
         </is>
       </c>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -3832,11 +4190,16 @@
           <t>4종</t>
         </is>
       </c>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="10" t="n"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>정기보험 제외</t>
         </is>
       </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -3849,11 +4212,16 @@
           <t>10분 전</t>
         </is>
       </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>암보험 M-CANCER-001</t>
         </is>
       </c>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
@@ -3861,6 +4229,13 @@
           <t xml:space="preserve">  ❑ 1. 보종별 MP DB 생성 현황</t>
         </is>
       </c>
+      <c r="B8" s="43" t="n"/>
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="43" t="n"/>
+      <c r="E8" s="43" t="n"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="43" t="n"/>
+      <c r="H8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -4157,6 +4532,13 @@
           <t xml:space="preserve">  ❑ 2. 보종별 VNB 예측 수행</t>
         </is>
       </c>
+      <c r="B47" s="43" t="n"/>
+      <c r="C47" s="43" t="n"/>
+      <c r="D47" s="43" t="n"/>
+      <c r="E47" s="43" t="n"/>
+      <c r="F47" s="43" t="n"/>
+      <c r="G47" s="43" t="n"/>
+      <c r="H47" s="44" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
@@ -4176,6 +4558,11 @@
           <t>보종 Select / 가입연령(숫자) / 성별(M/F) / 채널(GA/방카/TM/대면) / 가입금액(만원)</t>
         </is>
       </c>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="10" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
@@ -4188,6 +4575,11 @@
           <t>예측 VNB(억) / 신계약마진율(%) / 환산APE(만원)</t>
         </is>
       </c>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="10" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
@@ -4200,6 +4592,11 @@
           <t>정기보험 선택 시 '모델 미개발' 안내 + 예측 버튼 disabled</t>
         </is>
       </c>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="10" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
@@ -4212,15 +4609,20 @@
           <t>예측 ID / 보종 / 적용 모델 / VNB / 마진율 / 수행 시각</t>
         </is>
       </c>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="C51:H51"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="C50:H50"/>
     <mergeCell ref="C52:H52"/>
     <mergeCell ref="E4:H4"/>
@@ -4294,11 +4696,16 @@
           <t>599만</t>
         </is>
       </c>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
       <c r="E4" s="7" t="inlineStr">
         <is>
           <t>전체 보종 합산</t>
         </is>
       </c>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -4311,11 +4718,16 @@
           <t>38GB</t>
         </is>
       </c>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="10" t="n"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>TB_VNB_RESULT_* 합계</t>
         </is>
       </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -4328,11 +4740,16 @@
           <t>4종</t>
         </is>
       </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>정기보험 제외</t>
         </is>
       </c>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -4345,11 +4762,16 @@
           <t>10분 전</t>
         </is>
       </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="10" t="n"/>
       <c r="E7" s="7" t="inlineStr">
         <is>
           <t>암보험 결과</t>
         </is>
       </c>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="10" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
@@ -4357,6 +4779,13 @@
           <t xml:space="preserve">  ❑ 1. 보종별 MP 예측 결과 저장 현황</t>
         </is>
       </c>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
+      <c r="E9" s="43" t="n"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="43" t="n"/>
+      <c r="H9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
@@ -4613,6 +5042,13 @@
           <t xml:space="preserve">  ❑ 2. 보종별 VNB 집계 결과</t>
         </is>
       </c>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="43" t="n"/>
+      <c r="E43" s="43" t="n"/>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="n"/>
+      <c r="H43" s="44" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
@@ -4890,7 +5326,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>TAB 4: 예측모델 개발  (ModelDevTab)</t>
+          <t>TAB 4: VNB예측모델 개발  (ModelDevTab)</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
@@ -4901,12 +5337,20 @@
       <c r="G1" s="9" t="n"/>
       <c r="H1" s="10" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  ❑ 1. 보종별 예측 모델 구축 현황</t>
         </is>
       </c>
+      <c r="B3" s="43" t="n"/>
+      <c r="C3" s="43" t="n"/>
+      <c r="D3" s="43" t="n"/>
+      <c r="E3" s="43" t="n"/>
+      <c r="F3" s="43" t="n"/>
+      <c r="G3" s="43" t="n"/>
+      <c r="H3" s="44" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
@@ -5140,12 +5584,20 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  ❑ 2. 알고리즘 선정 후보</t>
         </is>
       </c>
+      <c r="B35" s="43" t="n"/>
+      <c r="C35" s="43" t="n"/>
+      <c r="D35" s="43" t="n"/>
+      <c r="E35" s="43" t="n"/>
+      <c r="F35" s="43" t="n"/>
+      <c r="G35" s="43" t="n"/>
+      <c r="H35" s="44" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
@@ -5187,6 +5639,10 @@
           <t>단순 선형 관계 가정, 기준선(Baseline) 역할</t>
         </is>
       </c>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="10" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="B39" s="24" t="inlineStr">
@@ -5204,6 +5660,10 @@
           <t>앙상블 기반, 과적합에 강건</t>
         </is>
       </c>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="10" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="B40" s="20" t="inlineStr">
@@ -5221,6 +5681,10 @@
           <t>부스팅 기반, 단기 시계열 예측 우수 → 암보험 채택</t>
         </is>
       </c>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="10" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="B41" s="24" t="inlineStr">
@@ -5238,6 +5702,10 @@
           <t>대용량 데이터 처리 속도 강점 → 종신·연금보험 채택</t>
         </is>
       </c>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="B42" s="20" t="inlineStr">
@@ -5255,13 +5723,25 @@
           <t>범주형 변수 자동 처리, 튜닝 부담 적음 → 건강보험 채택</t>
         </is>
       </c>
-    </row>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="10" t="n"/>
+    </row>
+    <row r="43"/>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  ❑ 3. 보종별 SHAP 영향도 분석</t>
         </is>
       </c>
+      <c r="B44" s="43" t="n"/>
+      <c r="C44" s="43" t="n"/>
+      <c r="D44" s="43" t="n"/>
+      <c r="E44" s="43" t="n"/>
+      <c r="F44" s="43" t="n"/>
+      <c r="G44" s="43" t="n"/>
+      <c r="H44" s="44" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
@@ -5281,6 +5761,11 @@
           <t>수평 BarChart (Recharts)</t>
         </is>
       </c>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="10" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
@@ -5293,6 +5778,11 @@
           <t>shapModel (기본: '암보험')</t>
         </is>
       </c>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="10" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
@@ -5305,6 +5795,11 @@
           <t>위험률, 해지율, 보험기간, 연령, 채널</t>
         </is>
       </c>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="10" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="12" t="inlineStr">
@@ -5317,6 +5812,11 @@
           <t>보험료대, 납기, 사업비율, 성별, 연령</t>
         </is>
       </c>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="10" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
@@ -5329,6 +5829,11 @@
           <t>예정이율, 가입금액, 납기, 연령, 성별</t>
         </is>
       </c>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="10" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
@@ -5341,13 +5846,26 @@
           <t>위험률, 특약수, 갱신주기, 연령, 채널</t>
         </is>
       </c>
-    </row>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="10" t="n"/>
+    </row>
+    <row r="52"/>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  ❑ 4. 재학습 체계</t>
         </is>
       </c>
+      <c r="B53" s="43" t="n"/>
+      <c r="C53" s="43" t="n"/>
+      <c r="D53" s="43" t="n"/>
+      <c r="E53" s="43" t="n"/>
+      <c r="F53" s="43" t="n"/>
+      <c r="G53" s="43" t="n"/>
+      <c r="H53" s="44" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
@@ -5550,6 +6068,10 @@
           <t xml:space="preserve">  ❑ 1. 집계 조회</t>
         </is>
       </c>
+      <c r="B3" s="43" t="n"/>
+      <c r="C3" s="43" t="n"/>
+      <c r="D3" s="43" t="n"/>
+      <c r="E3" s="44" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
@@ -5645,6 +6167,10 @@
           <t xml:space="preserve">  ❑ 2. 가입조건 VNB 시뮬레이션</t>
         </is>
       </c>
+      <c r="B11" s="43" t="n"/>
+      <c r="C11" s="43" t="n"/>
+      <c r="D11" s="43" t="n"/>
+      <c r="E11" s="44" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
@@ -5813,6 +6339,10 @@
           <t xml:space="preserve">  ❑ 3. 변경 영향 분석</t>
         </is>
       </c>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="43" t="n"/>
+      <c r="D24" s="43" t="n"/>
+      <c r="E24" s="44" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
@@ -6117,6 +6647,8 @@
           <t>집계 단위별(5종) 예측·결산 데이터 배열</t>
         </is>
       </c>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="10" t="n"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="B66" s="12" t="inlineStr">
@@ -6129,6 +6661,8 @@
           <t>보종별 기준 VNB + 9개 변수 영향 계수(coeff)</t>
         </is>
       </c>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="10" t="n"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="B67" s="12" t="inlineStr">
@@ -6141,6 +6675,8 @@
           <t>슬라이더 기본값 (gaRatio:30, femaleRatio:40, avgAge:42, payPeriod:20 등)</t>
         </is>
       </c>
+      <c r="D67" s="9" t="n"/>
+      <c r="E67" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -6179,7 +6715,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>TAB 6: 대시보드  (AggregationTab)</t>
+          <t>TAB 6: 대시보드  (AggregationTab) — 드래그앤드롭 위젯 그리드</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
@@ -6187,6 +6723,7 @@
       <c r="D1" s="9" t="n"/>
       <c r="E1" s="10" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -6209,11 +6746,13 @@
           <t>527억</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n"/>
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>전체 보종 합산</t>
         </is>
       </c>
+      <c r="E4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -6226,11 +6765,13 @@
           <t>514억</t>
         </is>
       </c>
+      <c r="C5" s="10" t="n"/>
       <c r="D5" s="7" t="inlineStr">
         <is>
           <t>전체 보종 합산</t>
         </is>
       </c>
+      <c r="E5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -6243,23 +6784,30 @@
           <t>4종</t>
         </is>
       </c>
+      <c r="C6" s="10" t="n"/>
       <c r="D6" s="7" t="inlineStr">
         <is>
           <t>정기보험 제외</t>
         </is>
       </c>
-    </row>
+      <c r="E6" s="10" t="n"/>
+    </row>
+    <row r="7"/>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❑ 1. VNB 결산 DB vs 예측 모델 트렌드</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ❑ 글로벌 필터 바</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="n"/>
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="43" t="n"/>
+      <c r="E8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ※ 보종 Select → 분기별 결산 DB vs 예측 모델 LineChart. 미래 분기는 예측 모델만(점선)</t>
+          <t xml:space="preserve">   ※ 대시보드 상단 콤보박스 필터. 기준분기(2024Q1~2025Q4) · 보종(전체/암/종신/연금/건강) · 채널(전체/GA/방카/TM/대면). 모든 위젯에 공통 적용</t>
         </is>
       </c>
     </row>
@@ -6271,9 +6819,11 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>trendCat (string, 기본값: '전체')</t>
-        </is>
-      </c>
+          <t>글로벌 필터: gCat(보종), gCh(채널), gQtr(분기)</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="10" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="B11" s="12" t="inlineStr">
@@ -6286,6 +6836,8 @@
           <t>Recharts LineChart</t>
         </is>
       </c>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="10" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="B12" s="12" t="inlineStr">
@@ -6298,6 +6850,8 @@
           <t>quarterlyTrend[trendCat] (2025Q1~2026Q2)</t>
         </is>
       </c>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="10" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="B13" s="12" t="inlineStr">
@@ -6310,18 +6864,25 @@
           <t>미래 분기 settlement=null → connectNulls=false</t>
         </is>
       </c>
-    </row>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14"/>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❑ 2. 동일가입조건 결산 DB vs 예측 모델 집계</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ❑ 위젯 그리드 (드래그앤드롭)</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="44" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ※ 보종 Select → 동일 MP 기준 결산 DB · 예측 모델 · 차이 · MAPE 비교 테이블</t>
+          <t xml:space="preserve">   ※ react-grid-layout(legacy)+WidthProvider 기반. 드래그(헤더≡)/리사이즈(우하단 핸들)/삭제(X버튼)/초기화(기본 위젯 3종 복원)</t>
         </is>
       </c>
     </row>
@@ -6333,9 +6894,11 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>cmpCat (기본: '암보험')</t>
-        </is>
-      </c>
+          <t>위젯 상태: widgets[] (id/kind/presetId/chartConfig/layout)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
@@ -6348,6 +6911,8 @@
           <t>conditionCompare[cmpCat]</t>
         </is>
       </c>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="10" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="B19" s="12" t="inlineStr">
@@ -6360,18 +6925,25 @@
           <t>가입조건(MP) / 결산 DB / 예측 모델 / 차이 / MAPE</t>
         </is>
       </c>
-    </row>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❑ 3. 원하는 조건으로 VNB 예측·집계</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ❑ 사용자 정의 차트 빌더</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="43" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="44" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ※ 가입조건 입력 → 보종별 예측 모델 VNB 산출 + 결산 DB 비교</t>
+          <t xml:space="preserve">   ※ "차트 추가" 버튼 → Step1 유형(막대/선형/면적/원형/히트맵) → Step2 축 구성(X:채널/보종/연령대/성별/납기/분기, Y:예측VNB/결산VNB/MAPE, 그룹차원) → 자동 제목 생성 후 그리드 추가</t>
         </is>
       </c>
     </row>
@@ -6386,6 +6958,8 @@
           <t>보종/채널/가입연령/성별/가입금액/보험기간/납기</t>
         </is>
       </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="10" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="B24" s="12" t="inlineStr">
@@ -6398,13 +6972,20 @@
           <t>결산 DB / 예측 모델 / 차이 / MAPE / 신계약마진율</t>
         </is>
       </c>
-    </row>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25"/>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❑ 4. 판매속성별 VNB 히트맵</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ❑ 판매속성별 VNB 히트맵</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="43" t="n"/>
+      <c r="D26" s="43" t="n"/>
+      <c r="E26" s="44" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
@@ -6424,6 +7005,8 @@
           <t>rowDim(기본:채널), colDim(기본:보종)</t>
         </is>
       </c>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="10" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
@@ -6436,6 +7019,8 @@
           <t>95 × DIM_WEIGHTS[rowDim][rowVal] × DIM_WEIGHTS[colDim][colVal]</t>
         </is>
       </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="10" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="B30" s="12" t="inlineStr">
@@ -6448,6 +7033,8 @@
           <t>bg-blue-50~bg-blue-800 9단계</t>
         </is>
       </c>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -6517,6 +7104,10 @@
           <t xml:space="preserve">  ❑ 1. 출력 설정</t>
         </is>
       </c>
+      <c r="B4" s="43" t="n"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="44" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
@@ -6683,6 +7274,10 @@
           <t xml:space="preserve">  ❑ 2. 결과 미리보기</t>
         </is>
       </c>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="44" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
@@ -6769,6 +7364,10 @@
           <t xml:space="preserve">  ❑ 3. 출력 이력</t>
         </is>
       </c>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="43" t="n"/>
+      <c r="D22" s="43" t="n"/>
+      <c r="E22" s="44" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
